--- a/Employee_Reports_wi52/Noel Jarabe Riego Q0165.xlsx
+++ b/Employee_Reports_wi52/Noel Jarabe Riego Q0165.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
+        <bgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +83,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -457,7 +463,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -548,16 +554,16 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>EXPIRING SOON</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr"/>
